--- a/academias/Matemáticas - Estadisticos 20241.xlsx
+++ b/academias/Matemáticas - Estadisticos 20241.xlsx
@@ -679,25 +679,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -746,25 +746,25 @@
         <v>125</v>
       </c>
       <c r="E6">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>74.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="H6" s="1">
-        <v>25.6</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>22.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -781,25 +781,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="H7" s="1">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2">
         <v>6.2</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -988,25 +988,25 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F13">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1">
-        <v>57.6</v>
+        <v>58.2</v>
       </c>
       <c r="H13" s="1">
-        <v>42.4</v>
+        <v>41.8</v>
       </c>
       <c r="I13" s="2">
         <v>6.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2014,25 +2014,25 @@
         <v>988</v>
       </c>
       <c r="E43">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="F43">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="G43" s="1">
-        <v>79.3</v>
+        <v>82</v>
       </c>
       <c r="H43" s="1">
-        <v>20.7</v>
+        <v>18</v>
       </c>
       <c r="I43" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J43">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2100,25 +2100,25 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2135,25 +2135,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2170,25 +2170,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2205,25 +2205,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2237,25 +2237,25 @@
         <v>125</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F6">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2272,25 +2272,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2307,25 +2307,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>32.4</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2342,25 +2342,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>30.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2377,25 +2377,25 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>52.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>47.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2412,25 +2412,25 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2447,25 +2447,25 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>47.6</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2479,25 +2479,25 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F13">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>31.8</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2514,25 +2514,25 @@
         <v>28</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2549,25 +2549,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2584,25 +2584,25 @@
         <v>34</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2619,25 +2619,25 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J17">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2654,25 +2654,25 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2689,25 +2689,25 @@
         <v>36</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2721,25 +2721,25 @@
         <v>210</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="F20">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J20">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2756,25 +2756,25 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2788,25 +2788,25 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2823,25 +2823,25 @@
         <v>20</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2858,25 +2858,25 @@
         <v>18</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>27.8</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2893,25 +2893,25 @@
         <v>23</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J25">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2928,25 +2928,25 @@
         <v>25</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2960,25 +2960,25 @@
         <v>86</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F27">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>11.6</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2995,25 +2995,25 @@
         <v>25</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J28">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3030,25 +3030,25 @@
         <v>19</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3065,25 +3065,25 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3100,25 +3100,25 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3132,25 +3132,25 @@
         <v>75</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F32">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J32">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3167,25 +3167,25 @@
         <v>36</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F33">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J33">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3199,25 +3199,25 @@
         <v>36</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F34">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J34">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3234,25 +3234,25 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F35">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3269,25 +3269,25 @@
         <v>41</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F36">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J36">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3304,25 +3304,25 @@
         <v>48</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F37">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>14.6</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J37">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3339,25 +3339,25 @@
         <v>37</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F38">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J38">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3409,25 +3409,25 @@
         <v>35</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F40">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J40">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3476,25 +3476,25 @@
         <v>258</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F42">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>67.8</v>
       </c>
       <c r="H42" s="1">
-        <v>100</v>
+        <v>32.2</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J42">
-        <v>258</v>
+        <v>57</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3505,25 +3505,25 @@
         <v>988</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="F43">
-        <v>988</v>
+        <v>167</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H43" s="1">
-        <v>100</v>
+        <v>16.9</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J43">
-        <v>988</v>
+        <v>57</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -3591,19 +3591,19 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H2" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3661,25 +3661,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3728,25 +3728,25 @@
         <v>125</v>
       </c>
       <c r="E6">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>74.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="H6" s="1">
-        <v>25.6</v>
+        <v>4</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>22.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3763,25 +3763,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>62.5</v>
+        <v>82.5</v>
       </c>
       <c r="H7" s="1">
-        <v>37.5</v>
+        <v>17.5</v>
       </c>
       <c r="I7" s="2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3810,7 +3810,7 @@
         <v>32.4</v>
       </c>
       <c r="I8" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3833,19 +3833,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>45.5</v>
+        <v>69.7</v>
       </c>
       <c r="H9" s="1">
-        <v>54.5</v>
+        <v>30.3</v>
       </c>
       <c r="I9" s="2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3868,19 +3868,19 @@
         <v>23</v>
       </c>
       <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
         <v>11</v>
       </c>
-      <c r="F10">
-        <v>12</v>
-      </c>
       <c r="G10" s="1">
+        <v>52.2</v>
+      </c>
+      <c r="H10" s="1">
         <v>47.8</v>
       </c>
-      <c r="H10" s="1">
-        <v>52.2</v>
-      </c>
       <c r="I10" s="2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3903,19 +3903,19 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="I11" s="2">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>52.4</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3970,25 +3970,25 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="F13">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G13" s="1">
-        <v>57.6</v>
+        <v>68.2</v>
       </c>
       <c r="H13" s="1">
-        <v>42.4</v>
+        <v>31.8</v>
       </c>
       <c r="I13" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4005,19 +4005,19 @@
         <v>28</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>82.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4087,7 +4087,7 @@
         <v>5.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4110,19 +4110,19 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4145,19 +4145,19 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4212,19 +4212,19 @@
         <v>210</v>
       </c>
       <c r="E20">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>91.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="H20" s="1">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4247,19 +4247,19 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I21" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4279,19 +4279,19 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4314,19 +4314,19 @@
         <v>20</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H23" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I23" s="2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4349,19 +4349,19 @@
         <v>18</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>61.1</v>
+        <v>72.2</v>
       </c>
       <c r="H24" s="1">
-        <v>38.9</v>
+        <v>27.8</v>
       </c>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4419,19 +4419,19 @@
         <v>25</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4451,19 +4451,19 @@
         <v>86</v>
       </c>
       <c r="E27">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>76.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="I27" s="2">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4486,19 +4486,19 @@
         <v>25</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="H28" s="1">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4533,7 +4533,7 @@
         <v>10.5</v>
       </c>
       <c r="I29" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4556,19 +4556,19 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4591,19 +4591,19 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4623,19 +4623,19 @@
         <v>75</v>
       </c>
       <c r="E32">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F32">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>76</v>
+        <v>90.7</v>
       </c>
       <c r="H32" s="1">
-        <v>24</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I32" s="2">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>36</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>83.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="I33" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4690,19 +4690,19 @@
         <v>36</v>
       </c>
       <c r="E34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>83.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="I34" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4737,7 +4737,7 @@
         <v>17.5</v>
       </c>
       <c r="I35" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4760,19 +4760,19 @@
         <v>41</v>
       </c>
       <c r="E36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
-        <v>85.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H36" s="1">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="I36" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4807,7 +4807,7 @@
         <v>14.6</v>
       </c>
       <c r="I37" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4830,19 +4830,19 @@
         <v>37</v>
       </c>
       <c r="E38">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1">
-        <v>78.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="H38" s="1">
-        <v>21.6</v>
+        <v>13.5</v>
       </c>
       <c r="I38" s="2">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4900,19 +4900,19 @@
         <v>35</v>
       </c>
       <c r="E40">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" s="1">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="H40" s="1">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I40" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4967,19 +4967,19 @@
         <v>258</v>
       </c>
       <c r="E42">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F42">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G42" s="1">
-        <v>85.3</v>
+        <v>87.2</v>
       </c>
       <c r="H42" s="1">
-        <v>14.7</v>
+        <v>12.8</v>
       </c>
       <c r="I42" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -4996,25 +4996,25 @@
         <v>988</v>
       </c>
       <c r="E43">
-        <v>783</v>
+        <v>871</v>
       </c>
       <c r="F43">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="G43" s="1">
-        <v>79.3</v>
+        <v>88.2</v>
       </c>
       <c r="H43" s="1">
-        <v>20.7</v>
+        <v>11.8</v>
       </c>
       <c r="I43" s="2">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="J43">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20241.xlsx
+++ b/academias/Matemáticas - Estadisticos 20241.xlsx
@@ -3374,25 +3374,25 @@
         <v>33</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F39">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>6.1</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J39">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3444,25 +3444,25 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F41">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J41">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3476,25 +3476,25 @@
         <v>258</v>
       </c>
       <c r="E42">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="F42">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="G42" s="1">
-        <v>67.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>32.2</v>
+        <v>12.4</v>
       </c>
       <c r="I42" s="2">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="J42">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>22.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3505,25 +3505,25 @@
         <v>988</v>
       </c>
       <c r="E43">
-        <v>821</v>
+        <v>872</v>
       </c>
       <c r="F43">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="G43" s="1">
-        <v>83.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="H43" s="1">
-        <v>16.9</v>
+        <v>11.7</v>
       </c>
       <c r="I43" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J43">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>5.8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4877,7 +4877,7 @@
         <v>6.1</v>
       </c>
       <c r="I39" s="2">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4935,19 +4935,19 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1">
-        <v>79.2</v>
+        <v>83.3</v>
       </c>
       <c r="H41" s="1">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="I41" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4967,19 +4967,19 @@
         <v>258</v>
       </c>
       <c r="E42">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F42">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G42" s="1">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="I42" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -4996,16 +4996,16 @@
         <v>988</v>
       </c>
       <c r="E43">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F43">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G43" s="1">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="H43" s="1">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="I43" s="2">
         <v>7.9</v>

--- a/academias/Matemáticas - Estadisticos 20241.xlsx
+++ b/academias/Matemáticas - Estadisticos 20241.xlsx
@@ -781,16 +781,16 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="H7" s="1">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="I7" s="2">
         <v>6.2</v>
@@ -851,19 +851,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="H9" s="1">
-        <v>54.5</v>
+        <v>51.5</v>
       </c>
       <c r="I9" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>52.2</v>
       </c>
       <c r="I10" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -988,19 +988,19 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F13">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G13" s="1">
-        <v>58.2</v>
+        <v>59.4</v>
       </c>
       <c r="H13" s="1">
-        <v>41.8</v>
+        <v>40.6</v>
       </c>
       <c r="I13" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1020,28 +1020,28 @@
         <v>34</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>23</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H14" s="1">
-        <v>17.9</v>
+        <v>20.7</v>
       </c>
       <c r="I14" s="2">
         <v>7.8</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1125,28 +1125,28 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E17">
         <v>35</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>87.5</v>
+        <v>79.5</v>
       </c>
       <c r="H17" s="1">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
       <c r="I17" s="2">
         <v>7.8</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1227,28 +1227,28 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E20">
         <v>193</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G20" s="1">
-        <v>91.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="H20" s="1">
-        <v>8.1</v>
+        <v>10.2</v>
       </c>
       <c r="I20" s="2">
         <v>8</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1329,28 +1329,28 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="H23" s="1">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1399,28 +1399,28 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>23</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I25" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1434,28 +1434,28 @@
         <v>44</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26">
         <v>22</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1">
-        <v>88</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>12</v>
+        <v>24.1</v>
       </c>
       <c r="I26" s="2">
         <v>7.2</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1466,28 +1466,28 @@
         <v>20</v>
       </c>
       <c r="D27">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E27">
         <v>66</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G27" s="1">
-        <v>76.7</v>
+        <v>71.7</v>
       </c>
       <c r="H27" s="1">
-        <v>23.3</v>
+        <v>28.3</v>
       </c>
       <c r="I27" s="2">
         <v>7</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2011,28 +2011,28 @@
         <v>23</v>
       </c>
       <c r="D43">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="E43">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F43">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G43" s="1">
-        <v>82</v>
+        <v>81.3</v>
       </c>
       <c r="H43" s="1">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="I43" s="2">
         <v>7.5</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K43" s="1">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -2511,28 +2511,28 @@
         <v>34</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>28</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I14" s="2">
         <v>9</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2616,28 +2616,28 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E17">
         <v>40</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I17" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2718,28 +2718,28 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E20">
         <v>208</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
-        <v>99</v>
+        <v>96.7</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="I20" s="2">
         <v>8.9</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2820,28 +2820,28 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>15</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="I23" s="2">
         <v>7.5</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2890,28 +2890,28 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>23</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I25" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2925,28 +2925,28 @@
         <v>44</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I26" s="2">
         <v>8.1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2957,28 +2957,28 @@
         <v>20</v>
       </c>
       <c r="D27">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E27">
         <v>76</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1">
-        <v>88.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>11.6</v>
+        <v>17.4</v>
       </c>
       <c r="I27" s="2">
         <v>8</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3502,28 +3502,28 @@
         <v>23</v>
       </c>
       <c r="D43">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="E43">
         <v>872</v>
       </c>
       <c r="F43">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G43" s="1">
-        <v>88.3</v>
+        <v>87.3</v>
       </c>
       <c r="H43" s="1">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="I43" s="2">
         <v>8</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K43" s="1">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -3591,19 +3591,19 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3661,19 +3661,19 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3696,19 +3696,19 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3728,19 +3728,19 @@
         <v>125</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>96</v>
+        <v>99.2</v>
       </c>
       <c r="H6" s="1">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>30.3</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3880,7 +3880,7 @@
         <v>47.8</v>
       </c>
       <c r="I10" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4002,28 +4002,28 @@
         <v>34</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>28</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4107,28 +4107,28 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="I17" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4209,28 +4209,28 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E20">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>99</v>
+        <v>95.8</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="I20" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4311,28 +4311,28 @@
         <v>41</v>
       </c>
       <c r="D23">
+        <v>21</v>
+      </c>
+      <c r="E23">
         <v>20</v>
       </c>
-      <c r="E23">
-        <v>15</v>
-      </c>
       <c r="F23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>75</v>
+        <v>95.2</v>
       </c>
       <c r="H23" s="1">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="I23" s="2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4349,19 +4349,19 @@
         <v>18</v>
       </c>
       <c r="E24">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4381,28 +4381,28 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>23</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4416,22 +4416,22 @@
         <v>44</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I26" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4448,28 +4448,28 @@
         <v>20</v>
       </c>
       <c r="D27">
+        <v>92</v>
+      </c>
+      <c r="E27">
         <v>86</v>
       </c>
-      <c r="E27">
-        <v>76</v>
-      </c>
       <c r="F27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1">
-        <v>88.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="H27" s="1">
-        <v>11.6</v>
+        <v>6.5</v>
       </c>
       <c r="I27" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4486,19 +4486,19 @@
         <v>25</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H28" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I28" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4521,19 +4521,19 @@
         <v>19</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H29" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I29" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4556,19 +4556,19 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I30" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4623,19 +4623,19 @@
         <v>75</v>
       </c>
       <c r="E32">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>90.7</v>
+        <v>94.7</v>
       </c>
       <c r="H32" s="1">
-        <v>9.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="I32" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4993,28 +4993,28 @@
         <v>23</v>
       </c>
       <c r="D43">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="E43">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="F43">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G43" s="1">
-        <v>88.3</v>
+        <v>88.8</v>
       </c>
       <c r="H43" s="1">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="I43" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K43" s="1">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20241.xlsx
+++ b/academias/Matemáticas - Estadisticos 20241.xlsx
@@ -3775,7 +3775,7 @@
         <v>17.5</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3798,19 +3798,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>67.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>32.4</v>
+        <v>17.6</v>
       </c>
       <c r="I8" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3833,19 +3833,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>69.7</v>
+        <v>75.8</v>
       </c>
       <c r="H9" s="1">
-        <v>30.3</v>
+        <v>24.2</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3903,19 +3903,19 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H11" s="1">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3970,19 +3970,19 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F13">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G13" s="1">
-        <v>68.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>31.8</v>
+        <v>27.1</v>
       </c>
       <c r="I13" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4247,19 +4247,19 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>96.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>3.6</v>
+        <v>17.9</v>
       </c>
       <c r="I21" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4279,19 +4279,19 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>96.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>3.6</v>
+        <v>17.9</v>
       </c>
       <c r="I22" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4795,19 +4795,19 @@
         <v>48</v>
       </c>
       <c r="E37">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" s="1">
-        <v>85.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="H37" s="1">
-        <v>14.6</v>
+        <v>4.2</v>
       </c>
       <c r="I37" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4877,7 +4877,7 @@
         <v>6.1</v>
       </c>
       <c r="I39" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4900,19 +4900,19 @@
         <v>35</v>
       </c>
       <c r="E40">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4935,19 +4935,19 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H41" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4967,16 +4967,16 @@
         <v>258</v>
       </c>
       <c r="E42">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="F42">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G42" s="1">
-        <v>87.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>12.4</v>
+        <v>8.1</v>
       </c>
       <c r="I42" s="2">
         <v>7.9</v>
@@ -4996,16 +4996,16 @@
         <v>999</v>
       </c>
       <c r="E43">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="F43">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G43" s="1">
-        <v>88.8</v>
+        <v>90.3</v>
       </c>
       <c r="H43" s="1">
-        <v>11.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I43" s="2">
         <v>7.8</v>

--- a/academias/Matemáticas - Estadisticos 20241.xlsx
+++ b/academias/Matemáticas - Estadisticos 20241.xlsx
@@ -3868,19 +3868,19 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>52.2</v>
+        <v>65.2</v>
       </c>
       <c r="H10" s="1">
-        <v>47.8</v>
+        <v>34.8</v>
       </c>
       <c r="I10" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3938,19 +3938,19 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>47.6</v>
+        <v>61.9</v>
       </c>
       <c r="H12" s="1">
-        <v>52.4</v>
+        <v>38.1</v>
       </c>
       <c r="I12" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3970,16 +3970,16 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G13" s="1">
-        <v>72.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="H13" s="1">
-        <v>27.1</v>
+        <v>23.5</v>
       </c>
       <c r="I13" s="2">
         <v>6.4</v>
@@ -4996,16 +4996,16 @@
         <v>999</v>
       </c>
       <c r="E43">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="F43">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G43" s="1">
-        <v>90.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H43" s="1">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I43" s="2">
         <v>7.8</v>

--- a/academias/Matemáticas - Estadisticos 20241.xlsx
+++ b/academias/Matemáticas - Estadisticos 20241.xlsx
@@ -1023,25 +1023,25 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>79.3</v>
+        <v>82.8</v>
       </c>
       <c r="H14" s="1">
-        <v>20.7</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1128,25 +1128,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>79.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>20.5</v>
+        <v>11.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1230,25 +1230,25 @@
         <v>215</v>
       </c>
       <c r="E20">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F20">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1">
-        <v>89.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>10.2</v>
+        <v>7.9</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1332,25 +1332,25 @@
         <v>21</v>
       </c>
       <c r="E23">
+        <v>11</v>
+      </c>
+      <c r="F23">
         <v>10</v>
       </c>
-      <c r="F23">
-        <v>11</v>
-      </c>
       <c r="G23" s="1">
+        <v>52.4</v>
+      </c>
+      <c r="H23" s="1">
         <v>47.6</v>
       </c>
-      <c r="H23" s="1">
-        <v>52.4</v>
-      </c>
       <c r="I23" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1402,25 +1402,25 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1437,25 +1437,25 @@
         <v>29</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G26" s="1">
-        <v>75.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="H26" s="1">
-        <v>24.1</v>
+        <v>10.3</v>
       </c>
       <c r="I26" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1469,25 +1469,25 @@
         <v>92</v>
       </c>
       <c r="E27">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1">
-        <v>71.7</v>
+        <v>78.3</v>
       </c>
       <c r="H27" s="1">
-        <v>28.3</v>
+        <v>21.7</v>
       </c>
       <c r="I27" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2014,25 +2014,25 @@
         <v>999</v>
       </c>
       <c r="E43">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="F43">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="G43" s="1">
-        <v>81.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H43" s="1">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
       <c r="I43" s="2">
         <v>7.5</v>
       </c>
       <c r="J43">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2514,25 +2514,25 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
         <v>9</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2619,25 +2619,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2721,25 +2721,25 @@
         <v>215</v>
       </c>
       <c r="E20">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>96.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="I20" s="2">
         <v>8.9</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2823,25 +2823,25 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>71.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="H23" s="1">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="2">
         <v>7.5</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2893,25 +2893,25 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2928,25 +2928,25 @@
         <v>29</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2960,25 +2960,25 @@
         <v>92</v>
       </c>
       <c r="E27">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F27">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>82.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>17.4</v>
+        <v>10.9</v>
       </c>
       <c r="I27" s="2">
         <v>8</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3505,25 +3505,25 @@
         <v>999</v>
       </c>
       <c r="E43">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="F43">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G43" s="1">
-        <v>87.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H43" s="1">
-        <v>12.7</v>
+        <v>11.6</v>
       </c>
       <c r="I43" s="2">
         <v>8</v>
       </c>
       <c r="J43">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4005,25 +4005,25 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4110,25 +4110,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="H17" s="1">
-        <v>13.6</v>
+        <v>4.5</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4212,25 +4212,25 @@
         <v>215</v>
       </c>
       <c r="E20">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>95.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="I20" s="2">
         <v>8.5</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4314,25 +4314,25 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4384,25 +4384,25 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
         <v>8.5</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4419,19 +4419,19 @@
         <v>29</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4451,25 +4451,25 @@
         <v>92</v>
       </c>
       <c r="E27">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4658,19 +4658,19 @@
         <v>36</v>
       </c>
       <c r="E33">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="I33" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4690,19 +4690,19 @@
         <v>36</v>
       </c>
       <c r="E34">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G34" s="1">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="I34" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4725,19 +4725,19 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>82.5</v>
+        <v>95</v>
       </c>
       <c r="H35" s="1">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4760,19 +4760,19 @@
         <v>41</v>
       </c>
       <c r="E36">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G36" s="1">
-        <v>87.8</v>
+        <v>92.7</v>
       </c>
       <c r="H36" s="1">
-        <v>12.2</v>
+        <v>7.3</v>
       </c>
       <c r="I36" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4830,19 +4830,19 @@
         <v>37</v>
       </c>
       <c r="E38">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="H38" s="1">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4967,16 +4967,16 @@
         <v>258</v>
       </c>
       <c r="E42">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F42">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1">
-        <v>91.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="H42" s="1">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="I42" s="2">
         <v>7.9</v>
@@ -4996,25 +4996,25 @@
         <v>999</v>
       </c>
       <c r="E43">
-        <v>908</v>
+        <v>934</v>
       </c>
       <c r="F43">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="G43" s="1">
-        <v>90.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="H43" s="1">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="I43" s="2">
         <v>7.8</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
